--- a/analysis/D55/ai-dlc/spreadsheets/AI-DLC Value Proposition Canvas.xlsx
+++ b/analysis/D55/ai-dlc/spreadsheets/AI-DLC Value Proposition Canvas.xlsx
@@ -471,7 +471,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>D55 AI Development Lifecycle Assessment</t>
+          <t>How to use AI in the Development Lifecycle — D55 Service Offering</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>AI Adoption &amp; Transformation</t>
+          <t>AI-Assisted Engineering</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Mid-market organisations (250-2000 employees) looking to adopt or scale AI</t>
+          <t>Mid-market engineering orgs (20-200 devs) who want to adopt AI-assisted development but are struggling with adoption, process change, or proving ROI</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -529,113 +529,116 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>No clear AI strategy — experimentation without business alignment</t>
+          <t>Bought Copilot licences but adoption is patchy — some devs love it, others ignore it</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Free AI-DLC Assessment: 1-hour structured workshop producing a radar chart of current vs target maturity across 8 dimensions</t>
+          <t>AI Tooling Rollout: standard configuration, shared skills/playbooks, MCP server setup, onboarding programme that gets every developer effective quickly</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Time to AI strategy: weeks → 1 hour
-Clarity of AI investment priorities</t>
+          <t>% daily active users
+Onboarding time (days → hours)
+Developer satisfaction score</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Tool sprawl — too many disconnected platforms, high onboarding time</t>
+          <t>Devs are faster but output quality is inconsistent — garbage specs at 5x speed</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Platform consolidation advisory + prescriptive tooling workshops for dev teams</t>
+          <t>AI-First Delivery Lifecycle Workshop: teach teams to spec for AI-first delivery. More time in design, contracts/APIs upfront, specs that AI can consume</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Tools touched per week
-New joiner productivity time
-Platform maintenance burden</t>
+          <t>Rework rate
+Defect density
+Spec-to-delivery ratio
+Time in design vs build</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>AI stays in notebooks — can't ship to production reliably</t>
+          <t>POs/BAs/PMs can't keep up — they've become the bottleneck now devs go 3-5x faster</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>MLOps implementation + CI/CD for models + observability</t>
+          <t>Process Redesign + Role Redefinition: adapt ceremonies, redefine coordination roles, introduce AI-assisted spec writing and prioritisation for the 'middle layer'</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Models in production
-Deployment frequency
-MTTR for model failures</t>
+          <t>Lead time (ticket → production)
+PR review wait time
+Sprint predictability</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>No visibility of AI spend or ROI — CFO can't justify investment</t>
+          <t>Can't prove ROI to the board/PE — 'it feels faster' but no hard numbers</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>FinOps programme + per-project cost allocation + ROI measurement framework</t>
+          <t>Measurement Framework + ROI Dashboard: define metrics, establish baseline, track before/after, package the investment case for finance/board/PE</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Cost per AI project
-ROI per initiative
-Budget forecast accuracy</t>
+          <t>Cycle time
+Deployment frequency
+Cost per feature
+Output per £ of eng cost</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Governance gap — no policy, no compliance posture, EU AI Act exposure</t>
+          <t>Governance gap — devs pasting prod data into AI tools, no policy, no audit trail</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>AI Governance framework + compliance posture review + region lockdown</t>
+          <t>AI Usage Policy + DLP Implementation: approved tool list, enterprise agreements, correct region, code provenance tracking, EU AI Act classification</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Audit readiness time
-Policy coverage
-Regulatory risk score</t>
+          <t>Policy compliance rate
+Data leakage incidents
+Audit readiness time</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Skills gap — dependent on heroes, no career path, can't recruit</t>
+          <t>Resistance from senior engineers and coordination roles — adoption stalling</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Embedded squads + training/upskilling + forward deployed engineers</t>
+          <t>Four Fears Diagnostic + Upskilling Programme: diagnose resistance patterns, tailor interventions per role, redefine value of coordination roles in AI-first world</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Bus factor
-Time to backfill
-Internal AI literacy rate</t>
+          <t>Adoption rate across roles
+Retention of key staff
+Time to productivity for new joiners</t>
         </is>
       </c>
     </row>
@@ -659,57 +662,57 @@
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Want AI to be a competitive differentiator, not just a cost play</t>
+          <t>Want engineering to be a competitive advantage — not just a cost centre</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>AI Strategy Workshop → Use Case Prioritisation → Business Case Development</t>
+          <t>8-Week Prove-It Model: embed D55 engineers in a squad, apply AI-first delivery on real work, demonstrate 3-5x improvement with metrics, produce rollout playbook</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Revenue from AI-enabled products
-Competitive win rate
-Time to market for AI features</t>
+          <t>Output per engineer (before/after)
+Release cadence
+Valuation multiple (PE angle)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Need to scale AI from 1-2 use cases to a portfolio</t>
+          <t>Need to scale AI-assisted development from one team to the whole org</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Discovery &amp; Strategy Session (DSD) producing a costed roadmap + runbook</t>
+          <t>Discovery &amp; Strategy Session: produce a costed roadmap for org-wide rollout. Identify blockers per team. Phase the transition. Build internal champions.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Active AI use cases
-Portfolio ROI
-Reuse of platform/data assets</t>
+          <t>% teams at Level 3+
+Org-wide productivity gain
+Rollout velocity (teams/quarter)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Want to embed AI literacy across the business, not just tech team</t>
+          <t>Want to attract and retain top engineering talent with AI-native ways of working</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>AI Champions Programme + Change Management + Ceremony/Process changes</t>
+          <t>AI-Native Engineering Culture: standard tooling, shared knowledge bases, community of practice, continuous skill evolution, public-facing AI engineering brand</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Non-tech AI tool adoption
-Ideas submitted from frontline
-Training completion rates</t>
+          <t>Offer acceptance rate
+Attrition rate
+Glassdoor/employer brand metrics</t>
         </is>
       </c>
     </row>
@@ -733,31 +736,31 @@
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>• AWS Advanced Partner with AI/ML specialisation
-• Proven delivery across data platforms, MLOps, and GenAI
-• Forward deployed engineers who build AND upskill
-• Free assessment lowers barrier to engagement
-• Prescriptive runbooks — not just advice, but a playbook</t>
+          <t>• We've actually shipped with AI-native teams at scale — not theory
+• We know what breaks when AI works (middle-layer bottleneck, spec quality, process)
+• Forward deployed engineers who build AND upskill — not a permanent dependency
+• 8-week prove-it model with metrics from day one
+• Free assessment lowers barrier — you see value before you spend</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>• EU AI Act compliance deadlines approaching
-• AI moving from experiment to board-level priority
-• Competitors adopting — window to differentiate closing
-• Cost pressure demands ROI visibility
-• Talent market means build-vs-buy decision is now</t>
+          <t>• AI developer tooling is mature enough to deliver 3-5x now (not 'soon')
+• Cost is trivial: ~£200/seat/month for 3-5x productivity
+• Competitors are adopting — delay is the real cost
+• EU AI Act compliance deadlines approaching
+• PE/board pressure for engineering efficiency gains</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>• AWS SageMaker Unified Studio
-• Bedrock / GenAI
-• Glue / Athena / Lakehouse
-• MLOps (SageMaker Pipelines, CodePipeline)
-• QuickSight
-• Infrastructure as Code (CDK/Terraform)
-• Kiro / AI-assisted development</t>
+          <t>• GitHub Copilot / Amazon CodeWhisperer / Amazon Q
+• Claude / Anthropic (agentic development)
+• Kiro / Cursor / agentic IDEs
+• MCP Servers (Jira, GitHub, DB integrations)
+• Playwright MCP (automated regression)
+• AWS CodePipeline / CI/CD
+• Infrastructure as Code (CDK/Terraform)</t>
         </is>
       </c>
     </row>
@@ -771,7 +774,7 @@
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Book an hour with us. We'll show you exactly where you are with AI, where you want to be, and what it takes to get there — for free. You leave with a radar chart, a gap analysis, and a clear roadmap. No commitment, just clarity. If you want us to help you execute, we've got workshops, embedded engineers, and runbooks ready to go.</t>
+          <t>Your developers have AI tools. But are they actually faster? Is the process adapted? Can you prove it? Book an hour with us — we'll assess your AI-assisted development readiness across 8 dimensions, show you where the gaps are, and tell you exactly what it takes to close them. Free. One hour. A radar chart and roadmap you can take to your board.</t>
         </is>
       </c>
     </row>
